--- a/data.xlsx
+++ b/data.xlsx
@@ -37,7 +37,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,12 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FA8DC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -90,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -112,12 +106,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -516,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB8"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5" outlineLevelCol="0"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -604,116 +592,116 @@
       </c>
     </row>
     <row r="2" ht="26.5" customHeight="1" thickBot="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>William</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>Andersen</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>2405 Sequoya Trail</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="n">
-        <v>72751</v>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>b.sophisticated@gmail.com</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>4794886150</v>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>1/20/1987</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>Pea Ridge</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="n"/>
-      <c r="M2" s="8" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Kathy</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Goldman</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>122 Clifton St</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>29649</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>sunshine29384@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>8643896859</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>36627</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Greenwood</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>submitted</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-18 22:06:53</t>
-        </is>
-      </c>
-      <c r="P2" s="8" t="inlineStr">
-        <is>
-          <t>k1bmsfc7</t>
-        </is>
-      </c>
-      <c r="Q2" s="8" t="n"/>
-      <c r="R2" s="8" t="n"/>
-      <c r="S2" s="8" t="n"/>
-      <c r="T2" s="8" t="n"/>
-      <c r="U2" s="8" t="n"/>
-      <c r="V2" s="8" t="n"/>
-      <c r="W2" s="8" t="n"/>
-      <c r="X2" s="8" t="n"/>
-      <c r="Y2" s="8" t="n"/>
-      <c r="Z2" s="8" t="n"/>
-      <c r="AA2" s="8" t="n"/>
-      <c r="AB2" s="8" t="n"/>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:16:21</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>k1bni5te</t>
+        </is>
+      </c>
+      <c r="Q2" s="7" t="n"/>
+      <c r="R2" s="7" t="n"/>
+      <c r="S2" s="7" t="n"/>
+      <c r="T2" s="7" t="n"/>
+      <c r="U2" s="7" t="n"/>
+      <c r="V2" s="7" t="n"/>
+      <c r="W2" s="7" t="n"/>
+      <c r="X2" s="7" t="n"/>
+      <c r="Y2" s="7" t="n"/>
+      <c r="Z2" s="7" t="n"/>
+      <c r="AA2" s="7" t="n"/>
+      <c r="AB2" s="7" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" thickBot="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Amos</t>
+          <t>Gwendolyn</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>1711 Hill St</t>
+          <t>231n Evergreen Ave Apt 16d</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>43525</v>
+        <v>8096</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>bighearted@mail.com</t>
+          <t>jahsi06@gmail.com</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>4198238608</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>27307</v>
+        <v>2153036807</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>1/28/1989</t>
+        </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -722,34 +710,34 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Haskins</t>
+          <t>Deptford</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>Submit was clicked but the lead form is still visible, so the row did not continue.</t>
         </is>
       </c>
       <c r="O3" s="7" t="inlineStr">
         <is>
-          <t>2026-04-18 22:06:53</t>
+          <t>2026-04-19 15:17:02</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
         <is>
-          <t>k1bmsfc6</t>
+          <t>k1bni5td</t>
         </is>
       </c>
       <c r="Q3" s="7" t="n"/>
@@ -765,71 +753,98 @@
       <c r="AA3" s="7" t="n"/>
       <c r="AB3" s="7" t="n"/>
     </row>
-    <row r="4" ht="26.5" customHeight="1" thickBot="1">
+    <row r="4" ht="15" customHeight="1" thickBot="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Rosalind</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Fisher</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>210 Highway 365</t>
+          <t>23414 Lahser Rd</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>15238</v>
+        <v>48033</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>t.straight@msn.com</t>
+          <t>hnurtho@aol.com</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>4124771181</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>32942</v>
+        <v>2482239789</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>3/20/1947</t>
+        </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Southfield</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t xml:space="preserve">Message: no such window: target window already closed
+from unknown error: web view not found
+  (Session info: chrome=144.0.7559.60)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff7032e6d35
+	0x7ff7032e6ce0
+	0x7ff703659cfd
+	0x7ff703628935
+	0x7ff7036e9e46
+	0x7ff703707954
+	0x7ff7036a7ef4
+	0x7ff7036a66fb
+	0x7ff7036a7bda
+	0x7ff703d477b6
+	0x7ff7032b9533
+	0x7ff703b57b3b
+	0x7ff703ceeb59
+	0x7ff70393af03
+	0x7ff70338a9fe
+	0x7ff70338a744
+	0x7ff70338a4b0
+	0x7ff7033a28fd
+	0x7ffe7d867374
+	0x7ffe7e09cc91
+</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>2026-04-18 22:06:53</t>
+          <t>2026-04-19 15:17:04</t>
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
-          <t>k1bmsfc5</t>
+          <t>k1bni5tc</t>
         </is>
       </c>
       <c r="Q4" s="7" t="n"/>
@@ -848,34 +863,32 @@
     <row r="5" ht="15" customHeight="1" thickBot="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Elvira</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Bayne</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>5406 Fleet</t>
+          <t>7756 Holmes</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>77517</v>
+        <v>48210</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>msverna@gmail.com</t>
+          <t>ms21_07@yahoo.com</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>4093541430</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>2/23/1970</t>
-        </is>
+        <v>3132850616</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>31474</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -884,17 +897,17 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Detroit</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -906,12 +919,12 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>2026-04-18 22:06:54</t>
+          <t>2026-04-19 15:16:20</t>
         </is>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>k1bmsfc4</t>
+          <t>k1bni5tb</t>
         </is>
       </c>
       <c r="Q5" s="7" t="n"/>
@@ -927,35 +940,37 @@
       <c r="AA5" s="7" t="n"/>
       <c r="AB5" s="7" t="n"/>
     </row>
-    <row r="6" ht="26.5" customHeight="1" thickBot="1">
+    <row r="6" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Homer</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Callier</t>
+          <t>Tobin</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2019 E 7th Ct</t>
+          <t>1043 Mockingbird Rd</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>98221</v>
+        <v>33873</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>brian.loman@gmail.com</t>
+          <t>etobin1971@live.com</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>3606611831</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>31629</v>
+        <v>8634481271</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>5/17/1971</t>
+        </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -964,17 +979,17 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Anacortes</t>
+          <t>Wauchula</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -986,12 +1001,12 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>2026-04-18 22:15:54</t>
+          <t>2026-04-19 15:23:32</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>k1bmt2sc</t>
+          <t>k1bni5t7</t>
         </is>
       </c>
       <c r="Q6" s="7" t="n"/>
@@ -1007,71 +1022,73 @@
       <c r="AA6" s="7" t="n"/>
       <c r="AB6" s="7" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" thickBot="1">
+    <row r="7" ht="26.5" customHeight="1" thickBot="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Janet</t>
+          <t>Byrd</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Lockhart</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2033 W 111th 2n</t>
+          <t>1528 Lincoln</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>94606</v>
+        <v>48146</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>janeth@live.com</t>
+          <t>dedabug66@yahoo.com</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>5102959191</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>32058</v>
+        <v>3136768275</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>1/22/2004</t>
+        </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>f</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Oakland</t>
+          <t>Lincoln Park</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>Submit was clicked but the lead form is still visible, so the row did not continue.</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>2026-04-18 22:16:36</t>
+          <t>2026-04-19 15:23:32</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>k1bmt2sa</t>
+          <t>k1bni5t6</t>
         </is>
       </c>
       <c r="Q7" s="7" t="n"/>
@@ -1087,37 +1104,35 @@
       <c r="AA7" s="7" t="n"/>
       <c r="AB7" s="7" t="n"/>
     </row>
-    <row r="8" ht="26.5" customHeight="1" thickBot="1">
+    <row r="8" ht="15" customHeight="1" thickBot="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>Velvet</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Pardo</t>
+          <t>Jennings</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>918 Gerald St</t>
+          <t>7 Jadewood Ln</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>19335</v>
+        <v>24333</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>jipardo@live.com</t>
+          <t>chj_2007@yahoo.com</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>6103482892</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>7/22/1973</t>
-        </is>
+        <v>2762331912</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>22555</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -1126,19 +1141,19 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Downingtown</t>
+          <t>Galax</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -1148,12 +1163,12 @@
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>2026-04-18 22:16:39</t>
+          <t>2026-04-19 15:24:19</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>k1bmt435</t>
+          <t>k1bni5t5</t>
         </is>
       </c>
       <c r="Q8" s="7" t="n"/>
@@ -1169,6 +1184,1706 @@
       <c r="AA8" s="7" t="n"/>
       <c r="AB8" s="7" t="n"/>
     </row>
+    <row r="9" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Carmen</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Rutherford</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>4238 N 30th St</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>53216</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>carmenrutherford@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4144602120</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>7/24/1974</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Milwaukee</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:23:32</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>k1bni5t4</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="n"/>
+      <c r="R9" s="7" t="n"/>
+      <c r="S9" s="7" t="n"/>
+      <c r="T9" s="7" t="n"/>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
+      <c r="W9" s="7" t="n"/>
+      <c r="X9" s="7" t="n"/>
+      <c r="Y9" s="7" t="n"/>
+      <c r="Z9" s="7" t="n"/>
+      <c r="AA9" s="7" t="n"/>
+      <c r="AB9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Sandy</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>123 Chalet Dr</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>29645</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>sandycunningham14@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>8648760265</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>28806</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Gray Court</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>Submit was clicked but the lead form is still visible, so the row did not continue.</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:24:13</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>k1bni5t3</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="n"/>
+      <c r="R10" s="7" t="n"/>
+      <c r="S10" s="7" t="n"/>
+      <c r="T10" s="7" t="n"/>
+      <c r="U10" s="7" t="n"/>
+      <c r="V10" s="7" t="n"/>
+      <c r="W10" s="7" t="n"/>
+      <c r="X10" s="7" t="n"/>
+      <c r="Y10" s="7" t="n"/>
+      <c r="Z10" s="7" t="n"/>
+      <c r="AA10" s="7" t="n"/>
+      <c r="AB10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" thickBot="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Kimberly</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Gilliam</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>706west12th</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>71635</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>gilliam809@gmail.com</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>8703649597</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>12/13/1979</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Crossett</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:34:21</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>k1bni5t2</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="n"/>
+      <c r="R11" s="7" t="n"/>
+      <c r="S11" s="7" t="n"/>
+      <c r="T11" s="7" t="n"/>
+      <c r="U11" s="7" t="n"/>
+      <c r="V11" s="7" t="n"/>
+      <c r="W11" s="7" t="n"/>
+      <c r="X11" s="7" t="n"/>
+      <c r="Y11" s="7" t="n"/>
+      <c r="Z11" s="7" t="n"/>
+      <c r="AA11" s="7" t="n"/>
+      <c r="AB11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Mcnealy</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Janice</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2001 Belle Vue Way H64</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>32304</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>jaiele1@aol.com</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>8505442350</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>6/25/1983</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Tallahassee</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:34:20</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>k1bni5sy</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="n"/>
+      <c r="R12" s="7" t="n"/>
+      <c r="S12" s="7" t="n"/>
+      <c r="T12" s="7" t="n"/>
+      <c r="U12" s="7" t="n"/>
+      <c r="V12" s="7" t="n"/>
+      <c r="W12" s="7" t="n"/>
+      <c r="X12" s="7" t="n"/>
+      <c r="Y12" s="7" t="n"/>
+      <c r="Z12" s="7" t="n"/>
+      <c r="AA12" s="7" t="n"/>
+      <c r="AB12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" thickBot="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Arielle</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>12044 Terry</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>48227</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>arielle627@gmail.com</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3132054384</v>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>9/21/1989</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:51:52</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>k1bnisuq</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="7" t="n"/>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
+      <c r="W13" s="7" t="n"/>
+      <c r="X13" s="7" t="n"/>
+      <c r="Y13" s="7" t="n"/>
+      <c r="Z13" s="7" t="n"/>
+      <c r="AA13" s="7" t="n"/>
+      <c r="AB13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" thickBot="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Shameka</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Wade</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>1026 46st</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>53140</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>carsonshameka@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>2627641366</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>29255</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Kenosha</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:43:46</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>k1bnisuv</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="7" t="n"/>
+      <c r="S14" s="7" t="n"/>
+      <c r="T14" s="7" t="n"/>
+      <c r="U14" s="7" t="n"/>
+      <c r="V14" s="7" t="n"/>
+      <c r="W14" s="7" t="n"/>
+      <c r="X14" s="7" t="n"/>
+      <c r="Y14" s="7" t="n"/>
+      <c r="Z14" s="7" t="n"/>
+      <c r="AA14" s="7" t="n"/>
+      <c r="AB14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" thickBot="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Christal</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Hart</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>809 Lee 507</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>72360</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>christal72360@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>8702951349</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>12/25/1983</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Marianna</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:43:47</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>k1bnisuu</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="n"/>
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="7" t="n"/>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
+      <c r="W15" s="7" t="n"/>
+      <c r="X15" s="7" t="n"/>
+      <c r="Y15" s="7" t="n"/>
+      <c r="Z15" s="7" t="n"/>
+      <c r="AA15" s="7" t="n"/>
+      <c r="AB15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" thickBot="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Luster</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>119 Alhambra Blvd</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>29673</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>step0214@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>8644517066</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>2/14/1973</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Piedmont</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:43:47</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>k1bnisus</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="n"/>
+      <c r="R16" s="7" t="n"/>
+      <c r="S16" s="7" t="n"/>
+      <c r="T16" s="7" t="n"/>
+      <c r="U16" s="7" t="n"/>
+      <c r="V16" s="7" t="n"/>
+      <c r="W16" s="7" t="n"/>
+      <c r="X16" s="7" t="n"/>
+      <c r="Y16" s="7" t="n"/>
+      <c r="Z16" s="7" t="n"/>
+      <c r="AA16" s="7" t="n"/>
+      <c r="AB16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Geri</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Pettus</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>865 37th Ave</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>94121</v>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>nopner@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>4157501957</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>7/26/1951</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:51:12</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>k1bnisup</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="n"/>
+      <c r="R17" s="7" t="n"/>
+      <c r="S17" s="7" t="n"/>
+      <c r="T17" s="7" t="n"/>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
+      <c r="W17" s="7" t="n"/>
+      <c r="X17" s="7" t="n"/>
+      <c r="Y17" s="7" t="n"/>
+      <c r="Z17" s="7" t="n"/>
+      <c r="AA17" s="7" t="n"/>
+      <c r="AB17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Naomah</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Mccoy</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>386 Miracle Ln</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>24224</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>lavenderski@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2767949580</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>29562</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Castlewood</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: Element not found for selectors: id=address
+</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:51:42</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>k1bnisun</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="n"/>
+      <c r="R18" s="7" t="n"/>
+      <c r="S18" s="7" t="n"/>
+      <c r="T18" s="7" t="n"/>
+      <c r="U18" s="7" t="n"/>
+      <c r="V18" s="7" t="n"/>
+      <c r="W18" s="7" t="n"/>
+      <c r="X18" s="7" t="n"/>
+      <c r="Y18" s="7" t="n"/>
+      <c r="Z18" s="7" t="n"/>
+      <c r="AA18" s="7" t="n"/>
+      <c r="AB18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Christina</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Cager</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>39 Las Flores</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>91910</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>christinacager@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>6197881693</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>3/27/2004</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Chula Vista</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: stale element reference: stale element not found
+  (Session info: chrome=146.0.7680.80); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#staleelementreferenceexception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7d0e58125+f4d5]
+	chromedriver!(No symbol) [0x7ff7d0ca77a7]
+	chromedriver!(No symbol) [0x7ff7d08dc2ee]
+	chromedriver!(No symbol) [0x7ff7d08f1a9b]
+	chromedriver!(No symbol) [0x7ff7d08f043b]
+	chromedriver!(No symbol) [0x7ff7d08e41af]
+	chromedriver!(No symbol) [0x7ff7d08e4153]
+	chromedriver!(No symbol) [0x7ff7d08e28ee]
+	chromedriver!(No symbol) [0x7ff7d08e6bde]
+	chromedriver!(No symbol) [0x7ff7d098305b]
+	chromedriver!(No symbol) [0x7ff7d095da9a]
+	chromedriver!(No symbol) [0x7ff7d092759c]
+	chromedriver!(No symbol) [0x7ff7d09821d4]
+	chromedriver!(No symbol) [0x7ff7d092684e]
+	chromedriver!(No symbol) [0x7ff7d092550f]
+	chromedriver!(No symbol) [0x7ff7d092656c]
+	chromedriver!GetHandleVerifier [0x7ff7d0e7a19c+3154c]
+	chromedriver!sqlite3_dbdata_init [0x7ff7d11d2011+25d7b1]
+	chromedriver!sqlite3_dbdata_init [0x7ff7d11d1a04+25d1a4]
+	chromedriver!sqlite3_dbdata_init [0x7ff7d11cc33b+257adb]
+	chromedriver!sqlite3_dbdata_init [0x7ff7d11d28f8+25e098]
+	chromedriver!(No symbol) [0x7ff7d0cc599e]
+	chromedriver!(No symbol) [0x7ff7d0cb65f4]
+	chromedriver!(No symbol) [0x7ff7d0cb67a6]
+	chromedriver!(No symbol) [0x7ff7d0c92ded]
+	KERNEL32!BaseThreadInitThunk [0x7ffe7d867374+14]
+	ntdll!RtlUserThreadStart [0x7ffe7e09cc91+21]
+</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:52:41</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>k1bnisum</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="n"/>
+      <c r="R19" s="7" t="n"/>
+      <c r="S19" s="7" t="n"/>
+      <c r="T19" s="7" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
+      <c r="W19" s="7" t="n"/>
+      <c r="X19" s="7" t="n"/>
+      <c r="Y19" s="7" t="n"/>
+      <c r="Z19" s="7" t="n"/>
+      <c r="AA19" s="7" t="n"/>
+      <c r="AB19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Ronald</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Mack</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>4848 N 8 St</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>19120</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>rmack4857@gmail.com</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>2153245707</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>31998</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 15:51:16</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>k1bnisur</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="n"/>
+      <c r="R20" s="7" t="n"/>
+      <c r="S20" s="7" t="n"/>
+      <c r="T20" s="7" t="n"/>
+      <c r="U20" s="7" t="n"/>
+      <c r="V20" s="7" t="n"/>
+      <c r="W20" s="7" t="n"/>
+      <c r="X20" s="7" t="n"/>
+      <c r="Y20" s="7" t="n"/>
+      <c r="Z20" s="7" t="n"/>
+      <c r="AA20" s="7" t="n"/>
+      <c r="AB20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Randia</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>500 S 47th St</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>19143</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>rjjohns18@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>2673048068</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>32052</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="n"/>
+      <c r="O21" s="7" t="n"/>
+      <c r="P21" s="7" t="n"/>
+      <c r="Q21" s="7" t="n"/>
+      <c r="R21" s="7" t="n"/>
+      <c r="S21" s="7" t="n"/>
+      <c r="T21" s="7" t="n"/>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
+      <c r="W21" s="7" t="n"/>
+      <c r="X21" s="7" t="n"/>
+      <c r="Y21" s="7" t="n"/>
+      <c r="Z21" s="7" t="n"/>
+      <c r="AA21" s="7" t="n"/>
+      <c r="AB21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" thickBot="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Bibbs-wortham</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>13728 Hidden Mesa</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>92394</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>carolwortham@msn.com</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>7608434914</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>5/17/1954</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Victorville</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:17:42</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>k1bnisul</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="n"/>
+      <c r="R22" s="7" t="n"/>
+      <c r="S22" s="7" t="n"/>
+      <c r="T22" s="7" t="n"/>
+      <c r="U22" s="7" t="n"/>
+      <c r="V22" s="7" t="n"/>
+      <c r="W22" s="7" t="n"/>
+      <c r="X22" s="7" t="n"/>
+      <c r="Y22" s="7" t="n"/>
+      <c r="Z22" s="7" t="n"/>
+      <c r="AA22" s="7" t="n"/>
+      <c r="AB22" s="7" t="n"/>
+    </row>
+    <row r="23" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Brittney</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>583 Wyatt Ave</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>42431</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>britbaby83@gmail.com</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>2704522541</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>6/18/1983</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Madisonville</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:17:41</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>k1bnisuk</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="n"/>
+      <c r="R23" s="7" t="n"/>
+      <c r="S23" s="7" t="n"/>
+      <c r="T23" s="7" t="n"/>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="7" t="n"/>
+      <c r="W23" s="7" t="n"/>
+      <c r="X23" s="7" t="n"/>
+      <c r="Y23" s="7" t="n"/>
+      <c r="Z23" s="7" t="n"/>
+      <c r="AA23" s="7" t="n"/>
+      <c r="AB23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Brenda</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Chavez</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>94 Old Colchester Rd</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>6375</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>bchavez012778@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>8604391416</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>1/27/1978</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Quaker Hill</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: stale element reference: stale element not found
+  (Session info: chrome=145.0.7632.117); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#staleelementreferenceexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff645723745
+	0x7ff645572977
+	0x7ff6451ac1be
+	0x7ff6451c18fb
+	0x7ff6451c029b
+	0x7ff6451b404f
+	0x7ff6451b3ff3
+	0x7ff6451b278e
+	0x7ff6451b6a7e
+	0x7ff64525377b
+	0x7ff64522e5ba
+	0x7ff6451f76ec
+	0x7ff645252924
+	0x7ff6451f686e
+	0x7ff6451f552f
+	0x7ff6451f658c
+	0x7ff645745a15
+	0x7ff645a6a531
+	0x7ff645a69f24
+	0x7ff645a649f9
+	0x7ff645a6ae18
+	0x7ff64559068e
+	0x7ff6455817e4
+	0x7ff645581996
+	0x7ff64555e68f
+	0x7ffe7d867374
+	0x7ffe7e09cc91
+</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:18:39</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>k1bnisuj</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="n"/>
+      <c r="R24" s="7" t="n"/>
+      <c r="S24" s="7" t="n"/>
+      <c r="T24" s="7" t="n"/>
+      <c r="U24" s="7" t="n"/>
+      <c r="V24" s="7" t="n"/>
+      <c r="W24" s="7" t="n"/>
+      <c r="X24" s="7" t="n"/>
+      <c r="Y24" s="7" t="n"/>
+      <c r="Z24" s="7" t="n"/>
+      <c r="AA24" s="7" t="n"/>
+      <c r="AB24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" thickBot="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>4920 36th Ave</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>53144</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>aprilwhite41078@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>2624962910</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>28767</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Kenosha</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:30:28</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>k1bnk2t6</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="n"/>
+      <c r="R25" s="7" t="n"/>
+      <c r="S25" s="7" t="n"/>
+      <c r="T25" s="7" t="n"/>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
+      <c r="W25" s="7" t="n"/>
+      <c r="X25" s="7" t="n"/>
+      <c r="Y25" s="7" t="n"/>
+      <c r="Z25" s="7" t="n"/>
+      <c r="AA25" s="7" t="n"/>
+      <c r="AB25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Byron</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Mazariegos</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>1080 A Capp St</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>33973</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>turbiov12@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>4155959203</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>28380</v>
+      </c>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>San Franisco</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:30:27</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>k1bnk2t5</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="n"/>
+      <c r="R26" s="7" t="n"/>
+      <c r="S26" s="7" t="n"/>
+      <c r="T26" s="7" t="n"/>
+      <c r="U26" s="7" t="n"/>
+      <c r="V26" s="7" t="n"/>
+      <c r="W26" s="7" t="n"/>
+      <c r="X26" s="7" t="n"/>
+      <c r="Y26" s="7" t="n"/>
+      <c r="Z26" s="7" t="n"/>
+      <c r="AA26" s="7" t="n"/>
+      <c r="AB26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="26.5" customHeight="1" thickBot="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Danita</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>101 John Ave S</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>33973</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>dlbrown_81@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>8633977890</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>2/18/1981</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Lehigh Acres</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>Form validation blocked submit: PageForm | Email Address: A part followed by '@' should not contain the symbol '\'.</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:42:02</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>k1bnk2t0</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="n"/>
+      <c r="R27" s="7" t="n"/>
+      <c r="S27" s="7" t="n"/>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
+      <c r="W27" s="7" t="n"/>
+      <c r="X27" s="7" t="n"/>
+      <c r="Y27" s="7" t="n"/>
+      <c r="Z27" s="7" t="n"/>
+      <c r="AA27" s="7" t="n"/>
+      <c r="AB27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" thickBot="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Danielle</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Farrelll</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>3839 Buchanan</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>48208</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>cree_jalen_dorian@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>3139746858</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>11/26/1979</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message: no such window: target window already closed
+from unknown error: web view not found
+  (Session info: chrome=146.0.7680.80)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff7f3338125+f4d5]
+	chromedriver!(No symbol) [0x7ff7f31877a7]
+	chromedriver!(No symbol) [0x7ff7f2dbc2ee]
+	chromedriver!(No symbol) [0x7ff7f2d942ad]
+	chromedriver!(No symbol) [0x7ff7f2e46c97]
+	chromedriver!(No symbol) [0x7ff7f2e6169a]
+	chromedriver!(No symbol) [0x7ff7f2e0684e]
+	chromedriver!(No symbol) [0x7ff7f2e0550f]
+	chromedriver!(No symbol) [0x7ff7f2e0656c]
+	chromedriver!GetHandleVerifier [0x7ff7f335a19c+3154c]
+	chromedriver!sqlite3_dbdata_init [0x7ff7f36b2011+25d7b1]
+	chromedriver!sqlite3_dbdata_init [0x7ff7f36b1a04+25d1a4]
+	chromedriver!sqlite3_dbdata_init [0x7ff7f36ac33b+257adb]
+	chromedriver!sqlite3_dbdata_init [0x7ff7f36b28f8+25e098]
+	chromedriver!(No symbol) [0x7ff7f31a599e]
+	chromedriver!(No symbol) [0x7ff7f31965f4]
+	chromedriver!(No symbol) [0x7ff7f31967a6]
+	chromedriver!(No symbol) [0x7ff7f3172ded]
+	KERNEL32!BaseThreadInitThunk [0x7ffe7d867374+14]
+	ntdll!RtlUserThreadStart [0x7ffe7e09cc91+21]
+</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:41:50</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>k1bnk2sy</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="n"/>
+      <c r="R28" s="7" t="n"/>
+      <c r="S28" s="7" t="n"/>
+      <c r="T28" s="7" t="n"/>
+      <c r="U28" s="7" t="n"/>
+      <c r="V28" s="7" t="n"/>
+      <c r="W28" s="7" t="n"/>
+      <c r="X28" s="7" t="n"/>
+      <c r="Y28" s="7" t="n"/>
+      <c r="Z28" s="7" t="n"/>
+      <c r="AA28" s="7" t="n"/>
+      <c r="AB28" s="7" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
